--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484738_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484738_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0092</v>
+        <v>4.8672</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8001</v>
+        <v>5.6052</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7909</v>
+        <v>-0.738</v>
       </c>
       <c r="G2" t="n">
         <v>5.1435</v>
@@ -610,13 +610,13 @@
         <v>1.1322</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7901</v>
+        <v>0.6481</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8288</v>
+        <v>0.634</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0387</v>
+        <v>0.0142</v>
       </c>
       <c r="V2" t="n">
         <v>-0.9244</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2426</v>
+        <v>0.251</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0518</v>
+        <v>-0.1492</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2944</v>
+        <v>0.4002</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4613</v>
@@ -844,13 +844,13 @@
         <v>0.9435</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5191</v>
+        <v>0.5275</v>
       </c>
       <c r="T5" t="n">
-        <v>0.77</v>
+        <v>0.6726</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.251</v>
+        <v>-0.1451</v>
       </c>
       <c r="V5" t="n">
         <v>0.3736</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. VILAGRAN GONZALEZ</t>
+          <t>V. CAMBRA NADAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1129</v>
+        <v>-0.1662</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4685</v>
+        <v>-0.0588</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5814</v>
+        <v>-0.1074</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8109</v>
+        <v>0.2383</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8905999999999999</v>
+        <v>0.2598</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07969999999999999</v>
+        <v>-0.0216</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1652</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1581</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0071</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6457000000000001</v>
+        <v>0.2383</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7325</v>
+        <v>0.2598</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0868</v>
+        <v>-0.0216</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3774</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1322</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7548</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5502</v>
+        <v>-0.4044</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8288</v>
+        <v>-0.0588</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7213000000000001</v>
+        <v>-0.3456</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.249</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V. CAMBRA NADAL</t>
+          <t>A. VILAGRAN GONZALEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1926</v>
+        <v>-0.2672</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0588</v>
+        <v>-0.6634</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1338</v>
+        <v>0.3962</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2383</v>
+        <v>-0.8109</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2598</v>
+        <v>-0.8905999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0216</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0.1652</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-0.1581</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.0071</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2383</v>
+        <v>-0.6457000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2598</v>
+        <v>-0.7325</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0216</v>
+        <v>0.0868</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1322</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.7548</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4309</v>
+        <v>1.1701</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0588</v>
+        <v>0.634</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3721</v>
+        <v>0.5362</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.249</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.249</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. BARBERO LOPEZ</t>
+          <t>R. MAS GANDIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2063</v>
+        <v>-0.4498</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4031</v>
+        <v>-1.7412</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6094</v>
+        <v>1.2914</v>
       </c>
       <c r="G8" t="n">
-        <v>3.3872</v>
+        <v>0.6777</v>
       </c>
       <c r="H8" t="n">
-        <v>2.9864</v>
+        <v>0.0517</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4008</v>
+        <v>0.626</v>
       </c>
       <c r="J8" t="n">
-        <v>5.2889</v>
+        <v>0.5326</v>
       </c>
       <c r="K8" t="n">
-        <v>3.9145</v>
+        <v>0.4915</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3743</v>
+        <v>0.0411</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.9017</v>
+        <v>0.1451</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9281</v>
+        <v>-0.4398</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9735</v>
+        <v>0.5849</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.8305</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.7175</v>
+        <v>-1.887</v>
       </c>
       <c r="R8" t="n">
-        <v>1.887</v>
+        <v>1.1322</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7313</v>
+        <v>-0.3727</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8317</v>
+        <v>-0.3868</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1004</v>
+        <v>0.0142</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.4942</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4942</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. MAS GANDIA</t>
+          <t>I. BARBERO LOPEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3834</v>
+        <v>-0.8741</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4103</v>
+        <v>0.6824</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0269</v>
+        <v>-1.5565</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6777</v>
+        <v>3.3872</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0517</v>
+        <v>2.9864</v>
       </c>
       <c r="I9" t="n">
-        <v>0.626</v>
+        <v>0.4008</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5326</v>
+        <v>5.2889</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4915</v>
+        <v>3.9145</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0411</v>
+        <v>1.3743</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1451</v>
+        <v>-1.9017</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4398</v>
+        <v>-0.9281</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5849</v>
+        <v>-0.9735</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7548</v>
+        <v>-2.8305</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.887</v>
+        <v>-4.7175</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1322</v>
+        <v>1.887</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3063</v>
+        <v>0.0635</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0559</v>
+        <v>0.111</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2504</v>
+        <v>-0.0475</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.4942</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.4942</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. TAENO ELEZ</t>
+          <t>N. RAMOS CAMPOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4483</v>
+        <v>-1.1132</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8628</v>
+        <v>-1.2245</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.3111</v>
+        <v>0.1113</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5193</v>
+        <v>-0.9641999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>2.5027</v>
+        <v>0.7357</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.0221</v>
+        <v>-1.6999</v>
       </c>
       <c r="J10" t="n">
-        <v>1.8589</v>
+        <v>0.1477</v>
       </c>
       <c r="K10" t="n">
-        <v>3.5608</v>
+        <v>1.4368</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.7019</v>
+        <v>-1.2891</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.3782</v>
+        <v>-1.1119</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.058</v>
+        <v>-0.7012</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.3202</v>
+        <v>-0.4108</v>
       </c>
       <c r="P10" t="n">
+        <v>0.5661</v>
+      </c>
+      <c r="Q10" t="n">
         <v>-1.1322</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-3.0192</v>
-      </c>
       <c r="R10" t="n">
-        <v>1.887</v>
+        <v>1.6983</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3956</v>
+        <v>0.1903</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4761</v>
+        <v>-0.2401</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0805</v>
+        <v>0.4304</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.1924</v>
+        <v>-0.9054</v>
       </c>
       <c r="W10" t="n">
-        <v>1.547</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.7394</v>
+        <v>-0.9054</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>N. RAMOS CAMPOS</t>
+          <t>J. MOLINA LORENZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4722</v>
+        <v>-2.1273</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1602</v>
+        <v>-1.4176</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.312</v>
+        <v>-0.7097</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9641999999999999</v>
+        <v>0.0274</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7357</v>
+        <v>2.3071</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.6999</v>
+        <v>-2.2797</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1477</v>
+        <v>3.1424</v>
       </c>
       <c r="K11" t="n">
-        <v>1.4368</v>
+        <v>4.2103</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2891</v>
+        <v>-1.0679</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1119</v>
+        <v>-3.1151</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7012</v>
+        <v>-1.9032</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4108</v>
+        <v>-1.2118</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5661</v>
+        <v>-1.5096</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1322</v>
+        <v>-3.774</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6983</v>
+        <v>2.2644</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1686</v>
+        <v>-0.3433</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1758</v>
+        <v>-0.786</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0071</v>
+        <v>0.4427</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9054</v>
+        <v>-0.3018</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.9054</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. MOLINA LORENZ</t>
+          <t>M. TAENO ELEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5758</v>
+        <v>-2.2632</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8661</v>
+        <v>0.8628</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7097</v>
+        <v>-3.1259</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0274</v>
+        <v>-0.5193</v>
       </c>
       <c r="H12" t="n">
-        <v>2.3071</v>
+        <v>2.5027</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.2797</v>
+        <v>-3.0221</v>
       </c>
       <c r="J12" t="n">
-        <v>3.1424</v>
+        <v>1.8589</v>
       </c>
       <c r="K12" t="n">
-        <v>4.2103</v>
+        <v>3.5608</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.0679</v>
+        <v>-1.7019</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.1151</v>
+        <v>-2.3782</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.9032</v>
+        <v>-1.058</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.2118</v>
+        <v>-1.3202</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.5096</v>
+        <v>-1.1322</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.774</v>
+        <v>-3.0192</v>
       </c>
       <c r="R12" t="n">
-        <v>2.2644</v>
+        <v>1.887</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7917999999999999</v>
+        <v>0.5808</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2345</v>
+        <v>0.4761</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4427</v>
+        <v>0.1047</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3018</v>
+        <v>-1.1924</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.547</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.3018</v>
+        <v>-2.7394</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.1541</v>
+        <v>-3.6315</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.9577</v>
+        <v>-2.5092</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1964</v>
+        <v>-1.1223</v>
       </c>
       <c r="G13" t="n">
         <v>-0.7252999999999999</v>
@@ -1468,13 +1468,13 @@
         <v>1.5096</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7073</v>
+        <v>0.2299</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0582</v>
+        <v>-0.6097</v>
       </c>
       <c r="U13" t="n">
-        <v>1.7654</v>
+        <v>0.8395</v>
       </c>
       <c r="V13" t="n">
         <v>-0.8716</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.9323</v>
+        <v>-2.6386</v>
       </c>
       <c r="E14" t="n">
-        <v>2.228300000000001</v>
+        <v>2.522199999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-5.1606</v>
+        <v>-5.1607</v>
       </c>
       <c r="G14" t="n">
         <v>9.1288</v>
@@ -1537,22 +1537,22 @@
         <v>-3.6765</v>
       </c>
       <c r="P14" t="n">
-        <v>-8.491499999999998</v>
+        <v>-8.4915</v>
       </c>
       <c r="Q14" t="n">
-        <v>-21.7005</v>
+        <v>-21.70050000000001</v>
       </c>
       <c r="R14" t="n">
         <v>13.209</v>
       </c>
       <c r="S14" t="n">
-        <v>1.996</v>
+        <v>2.2898</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1522000000000006</v>
+        <v>0.4463</v>
       </c>
       <c r="U14" t="n">
-        <v>1.8434</v>
+        <v>1.8437</v>
       </c>
       <c r="V14" t="n">
         <v>-5.5652</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4703</v>
+        <v>2.9857</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2091</v>
+        <v>2.3066</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2611</v>
+        <v>0.6791</v>
       </c>
       <c r="G15" t="n">
         <v>-1.3377</v>
@@ -1624,13 +1624,13 @@
         <v>4.1514</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6949</v>
+        <v>0.2103</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3223</v>
+        <v>-0.2248</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0171</v>
+        <v>0.4351</v>
       </c>
       <c r="V15" t="n">
         <v>2.7922</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9663</v>
+        <v>2.1334</v>
       </c>
       <c r="E16" t="n">
-        <v>1.292</v>
+        <v>1.1945</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6743</v>
+        <v>0.9388</v>
       </c>
       <c r="G16" t="n">
         <v>-1.5317</v>
@@ -1702,13 +1702,13 @@
         <v>2.8305</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2569</v>
+        <v>-0.0898</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1706</v>
+        <v>-0.268</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0864</v>
+        <v>0.1782</v>
       </c>
       <c r="V16" t="n">
         <v>0.9244</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3039</v>
+        <v>1.7201</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2536</v>
+        <v>2.6433</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9497</v>
+        <v>-0.9232</v>
       </c>
       <c r="G17" t="n">
         <v>-0.9612000000000001</v>
@@ -1780,13 +1780,13 @@
         <v>2.4531</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4332</v>
+        <v>-1.017</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8695000000000001</v>
+        <v>-0.4797</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5637</v>
+        <v>-0.5372</v>
       </c>
       <c r="V17" t="n">
         <v>1.2452</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. ANTICH MINGUEZ</t>
+          <t>M. LOPEZ VILLENA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0392</v>
+        <v>0.5766</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4544</v>
+        <v>0.6297</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4152</v>
+        <v>-0.0531</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0015</v>
+        <v>0.5619</v>
       </c>
       <c r="H18" t="n">
-        <v>0.162</v>
+        <v>0.3021</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1605</v>
+        <v>0.2598</v>
       </c>
       <c r="J18" t="n">
-        <v>3.9617</v>
+        <v>0.6762</v>
       </c>
       <c r="K18" t="n">
-        <v>3.1703</v>
+        <v>0.6762</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7915</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.9603</v>
+        <v>-0.1143</v>
       </c>
       <c r="N18" t="n">
-        <v>-3.0083</v>
+        <v>-0.3741</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.952</v>
+        <v>0.2598</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.0757</v>
+        <v>0.1887</v>
       </c>
       <c r="Q18" t="n">
-        <v>-5.661</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.5853</v>
+        <v>0.1887</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2456</v>
+        <v>-0.174</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3614</v>
+        <v>-0.0465</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8842</v>
+        <v>-0.1276</v>
       </c>
       <c r="V18" t="n">
-        <v>1.8678</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.7922</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.9244</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. LOPEZ VILLENA</t>
+          <t>P. BELLVER VALIENTE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4972</v>
+        <v>0.4349</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6297</v>
+        <v>0.4101</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1325</v>
+        <v>0.0248</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5619</v>
+        <v>0.3135</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3021</v>
+        <v>-0.3772</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2598</v>
+        <v>0.6907</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6762</v>
+        <v>0.3792</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6762</v>
+        <v>0.3381</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.0411</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1143</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3741</v>
+        <v>-0.7153</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2598</v>
+        <v>0.6496</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1887</v>
+        <v>0.5661</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1887</v>
+        <v>0.5661</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2534</v>
+        <v>-0.4447</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0465</v>
+        <v>0.0308</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2069</v>
+        <v>-0.4756</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. BELLVER VALIENTE</t>
+          <t>P. ANTICH MINGUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2135</v>
+        <v>0.2165</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2152</v>
+        <v>0.8697</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0016</v>
+        <v>-0.6532</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3135</v>
+        <v>0.0015</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3772</v>
+        <v>0.162</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6907</v>
+        <v>-0.1605</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3792</v>
+        <v>3.9617</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3381</v>
+        <v>3.1703</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0411</v>
+        <v>0.7915</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.06569999999999999</v>
+        <v>-3.9603</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7153</v>
+        <v>-3.0083</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6496</v>
+        <v>-0.952</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5661</v>
+        <v>-2.0757</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-5.661</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5661</v>
+        <v>3.5853</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.666</v>
+        <v>0.4229</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.164</v>
+        <v>-0.2232</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.502</v>
+        <v>0.6461</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.8678</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.7922</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.9244</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. MORATA</t>
+          <t>O. CASTRILLON RODRIGUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0459</v>
+        <v>-0.2762</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8388</v>
+        <v>0.0571</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8847</v>
+        <v>-0.3333</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.4966</v>
+        <v>-1.0412</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8945</v>
+        <v>-1.2318</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.6021</v>
+        <v>0.1906</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2801</v>
+        <v>-0.4828</v>
       </c>
       <c r="K21" t="n">
-        <v>1.4955</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.7756</v>
+        <v>0.0823</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.2165</v>
+        <v>-0.5584</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.39</v>
+        <v>-0.6667999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1736</v>
+        <v>0.1083</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5096</v>
+        <v>0.7548</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4531</v>
+        <v>0.7548</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9411</v>
+        <v>0.3309</v>
       </c>
       <c r="T21" t="n">
-        <v>1.138</v>
+        <v>0.238</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1969</v>
+        <v>0.0929</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.3208</v>
       </c>
       <c r="W21" t="n">
-        <v>0.9244</v>
+        <v>0.3018</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.9244</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.205</v>
+        <v>-0.2844</v>
       </c>
       <c r="E22" t="n">
         <v>-0.7837</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5786</v>
+        <v>0.4993</v>
       </c>
       <c r="G22" t="n">
         <v>-0.8401999999999999</v>
@@ -2170,13 +2170,13 @@
         <v>0.1887</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1952</v>
+        <v>-0.2745</v>
       </c>
       <c r="T22" t="n">
         <v>-0.1764</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0188</v>
+        <v>-0.0982</v>
       </c>
       <c r="V22" t="n">
         <v>0.6415999999999999</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>O. CASTRILLON RODRIGUEZ</t>
+          <t>I. TRILLO SOUTO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2762</v>
+        <v>-0.7765</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0571</v>
+        <v>-0.746</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3333</v>
+        <v>-0.0305</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.0412</v>
+        <v>-0.6613</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.2318</v>
+        <v>-0.7912</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1906</v>
+        <v>0.1299</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.4828</v>
+        <v>-0.6284</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.6284</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0823</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5584</v>
+        <v>-0.0329</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6667999999999999</v>
+        <v>-0.1628</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1083</v>
+        <v>0.1299</v>
       </c>
       <c r="P23" t="n">
-        <v>0.7548</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.7548</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3309</v>
+        <v>-0.1152</v>
       </c>
       <c r="T23" t="n">
-        <v>0.238</v>
+        <v>-0.1176</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0929</v>
+        <v>0.0024</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3208</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.6226</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>I. TRILLO SOUTO</t>
+          <t>D. MARTINEZ JURADO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.8559</v>
+        <v>-0.7786999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.746</v>
+        <v>1.7807</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1099</v>
+        <v>-2.5594</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.6613</v>
+        <v>-0.3905</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.7912</v>
+        <v>-0.7998</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1299</v>
+        <v>0.4093</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6284</v>
+        <v>1.4357</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6284</v>
+        <v>1.3946</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>0.0411</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.0329</v>
+        <v>-1.8262</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1628</v>
+        <v>-2.1944</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1299</v>
+        <v>0.3682</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>0.9435</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>0.9435</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1946</v>
+        <v>-0.3883</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1176</v>
+        <v>0.0432</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.077</v>
+        <v>-0.4315</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-0.9434</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>D. MARTINEZ JURADO</t>
+          <t>E. MORATA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.0265</v>
+        <v>-0.8796</v>
       </c>
       <c r="E25" t="n">
-        <v>1.5858</v>
+        <v>-0.233</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.6123</v>
+        <v>-0.6466</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.3905</v>
+        <v>-2.4966</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.7998</v>
+        <v>-0.8945</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4093</v>
+        <v>-1.6021</v>
       </c>
       <c r="J25" t="n">
-        <v>1.4357</v>
+        <v>-0.2801</v>
       </c>
       <c r="K25" t="n">
-        <v>1.3946</v>
+        <v>1.4955</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0411</v>
+        <v>-1.7756</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.8262</v>
+        <v>-2.2165</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.1944</v>
+        <v>-2.39</v>
       </c>
       <c r="O25" t="n">
-        <v>0.3682</v>
+        <v>0.1736</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9435</v>
+        <v>1.5096</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9435</v>
+        <v>2.4531</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6361</v>
+        <v>0.1074</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1517</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4844</v>
+        <v>0.0412</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.9434</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0.3018</v>
+        <v>0.9244</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.2452</v>
+        <v>-0.9244</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.1484</v>
+        <v>-2.1392</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.8453</v>
+        <v>-2.9684</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6969</v>
+        <v>0.8292</v>
       </c>
       <c r="G26" t="n">
         <v>-0.745</v>
@@ -2482,13 +2482,13 @@
         <v>3.5853</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.5731</v>
+        <v>-0.5639</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.5626</v>
+        <v>-0.6857</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.0105</v>
+        <v>0.1218</v>
       </c>
       <c r="V26" t="n">
         <v>-0.6415999999999999</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>2.9325</v>
+        <v>2.932599999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>5.1607</v>
+        <v>5.1606</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.2283</v>
+        <v>-2.2281</v>
       </c>
       <c r="G27" t="n">
         <v>-9.128499999999999</v>
@@ -2536,7 +2536,7 @@
         <v>11.5727</v>
       </c>
       <c r="K27" t="n">
-        <v>7.896400000000002</v>
+        <v>7.8964</v>
       </c>
       <c r="L27" t="n">
         <v>3.6764</v>
@@ -2560,16 +2560,16 @@
         <v>21.7005</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.996</v>
+        <v>-1.9959</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.8438</v>
+        <v>-1.8437</v>
       </c>
       <c r="U27" t="n">
         <v>-0.1524000000000001</v>
       </c>
       <c r="V27" t="n">
-        <v>5.565399999999999</v>
+        <v>5.5654</v>
       </c>
       <c r="W27" t="n">
         <v>8.6404</v>
